--- a/04_DESIGN_TABLES/DesignTable_2650_SW2.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_2650_SW2.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CL5"/>
+  <dimension ref="A1:CL6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1157,32 +1157,32 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2650-06-06-06-06-FG</t>
+          <t>2650-04-04-04-04-FG</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.06</v>
+        <v>0.89</v>
       </c>
       <c r="C3" t="n">
-        <v>0.28125</v>
+        <v>0.22</v>
       </c>
       <c r="D3" t="n">
-        <v>0.28125</v>
+        <v>0.21875</v>
       </c>
       <c r="E3" t="n">
-        <v>0.083</v>
+        <v>0.075</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2515</v>
+        <v>0.2608</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2405</v>
+        <v>0.182</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0898</v>
+        <v>0.0795</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1082</v>
+        <v>0.1135</v>
       </c>
       <c r="J3" t="n">
         <v>60</v>
@@ -1191,28 +1191,28 @@
         <v>37</v>
       </c>
       <c r="L3" t="n">
-        <v>1.06</v>
+        <v>0.89</v>
       </c>
       <c r="M3" t="n">
-        <v>0.28125</v>
+        <v>0.22</v>
       </c>
       <c r="N3" t="n">
-        <v>0.28125</v>
+        <v>0.21875</v>
       </c>
       <c r="O3" t="n">
-        <v>0.083</v>
+        <v>0.075</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2515</v>
+        <v>0.2608</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.2405</v>
+        <v>0.182</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0898</v>
+        <v>0.0795</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1082</v>
+        <v>0.1135</v>
       </c>
       <c r="T3" t="n">
         <v>60</v>
@@ -1221,28 +1221,28 @@
         <v>37</v>
       </c>
       <c r="V3" t="n">
-        <v>1.06</v>
+        <v>0.89</v>
       </c>
       <c r="W3" t="n">
-        <v>0.28125</v>
+        <v>0.22</v>
       </c>
       <c r="X3" t="n">
-        <v>0.28125</v>
+        <v>0.21875</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.083</v>
+        <v>0.075</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.2515</v>
+        <v>0.2608</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.2405</v>
+        <v>0.182</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0898</v>
+        <v>0.0795</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.1082</v>
+        <v>0.1135</v>
       </c>
       <c r="AD3" t="n">
         <v>60</v>
@@ -1251,28 +1251,28 @@
         <v>37</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.06</v>
+        <v>0.89</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.28125</v>
+        <v>0.22</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.28125</v>
+        <v>0.21875</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.083</v>
+        <v>0.075</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.2515</v>
+        <v>0.2608</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.2405</v>
+        <v>0.182</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.0898</v>
+        <v>0.0795</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.1082</v>
+        <v>0.1135</v>
       </c>
       <c r="AN3" t="n">
         <v>60</v>
@@ -1281,127 +1281,127 @@
         <v>37</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.3</v>
+        <v>0.17</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.06</v>
+        <v>0.89</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.3</v>
+        <v>0.17</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.06</v>
+        <v>0.89</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.3</v>
+        <v>0.17</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.06</v>
+        <v>0.89</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.3</v>
+        <v>0.17</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.06</v>
+        <v>0.89</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.5625</v>
+        <v>0.4375</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.05556</v>
+        <v>0.05</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.2515</v>
+        <v>0.2608</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.03007</v>
+        <v>0.02706</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.01389</v>
+        <v>0.0125</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.05556</v>
+        <v>0.05</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.5625</v>
+        <v>0.4375</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.05556</v>
+        <v>0.05</v>
       </c>
       <c r="BF3" t="n">
-        <v>0.2515</v>
+        <v>0.2608</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.03007</v>
+        <v>0.02706</v>
       </c>
       <c r="BH3" t="n">
-        <v>0.01389</v>
+        <v>0.0125</v>
       </c>
       <c r="BI3" t="n">
-        <v>0.05556</v>
+        <v>0.05</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.5625</v>
+        <v>0.4375</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.05556</v>
+        <v>0.05</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.2515</v>
+        <v>0.2608</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.03007</v>
+        <v>0.02706</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.01389</v>
+        <v>0.0125</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.05556</v>
+        <v>0.05</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.5625</v>
+        <v>0.4375</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0.05556</v>
+        <v>0.05</v>
       </c>
       <c r="BR3" t="n">
-        <v>0.2515</v>
+        <v>0.2608</v>
       </c>
       <c r="BS3" t="n">
-        <v>0.03007</v>
+        <v>0.02706</v>
       </c>
       <c r="BT3" t="n">
-        <v>0.01389</v>
+        <v>0.0125</v>
       </c>
       <c r="BU3" t="n">
-        <v>0.05556</v>
+        <v>0.05</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.5625</v>
+        <v>0.44</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.504</v>
+        <v>0.34</v>
       </c>
       <c r="BX3" t="n">
-        <v>0.504</v>
+        <v>0.34</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.5625</v>
+        <v>0.44</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0.504</v>
+        <v>0.34</v>
       </c>
       <c r="CA3" t="n">
-        <v>0.504</v>
+        <v>0.34</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2650-06-06-06-06-FG</t>
+          <t>2650-04-04-04-04-FG</t>
         </is>
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>Union Cross, 9/16-18 JIC x 9/16-18 JIC x 9/16-18 JIC x 9/16-18 JIC</t>
+          <t>Union Cross, 7/16-20 JIC x 7/16-20 JIC x 7/16-20 JIC x 7/16-20 JIC</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
@@ -1411,27 +1411,27 @@
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>9/16-18 JIC</t>
+          <t>7/16-20 JIC</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>9/16-18 JIC</t>
+          <t>7/16-20 JIC</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>9/16-18 JIC</t>
+          <t>7/16-20 JIC</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>9/16-18 JIC</t>
+          <t>7/16-20 JIC</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
@@ -1441,44 +1441,44 @@
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> | hex A/F raised from Air-Way 0.56 to 0.5625 (JIC thread major; 2603HX rule)</t>
+          <t>DROP: Air-Way row with no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | Brennan TFA TFA-p062-t02: agrees on M1@DRIVE, M2@DRIVE, M3@DRIVE, M4@DRIVE, Y@HEX, D1@BORE, D2@BORE, D3@BORE, D4@BORE</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>2650-06-06-06-06-FG</t>
+          <t>2650-04-04-04-04-FG</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2650-12-12-12-12-FG</t>
+          <t>2650-06-06-06-06-FG</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.66</v>
+        <v>1.06</v>
       </c>
       <c r="C4" t="n">
-        <v>0.53125</v>
+        <v>0.28125</v>
       </c>
       <c r="D4" t="n">
-        <v>0.53125</v>
+        <v>0.28125</v>
       </c>
       <c r="E4" t="n">
-        <v>0.125</v>
+        <v>0.083</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3895</v>
+        <v>0.2515</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4715</v>
+        <v>0.2405</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1299</v>
+        <v>0.0898</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1851</v>
+        <v>0.1082</v>
       </c>
       <c r="J4" t="n">
         <v>60</v>
@@ -1487,28 +1487,28 @@
         <v>37</v>
       </c>
       <c r="L4" t="n">
-        <v>1.66</v>
+        <v>1.06</v>
       </c>
       <c r="M4" t="n">
-        <v>0.53125</v>
+        <v>0.28125</v>
       </c>
       <c r="N4" t="n">
-        <v>0.53125</v>
+        <v>0.28125</v>
       </c>
       <c r="O4" t="n">
-        <v>0.125</v>
+        <v>0.083</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3895</v>
+        <v>0.2515</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.4715</v>
+        <v>0.2405</v>
       </c>
       <c r="R4" t="n">
-        <v>0.1299</v>
+        <v>0.0898</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1851</v>
+        <v>0.1082</v>
       </c>
       <c r="T4" t="n">
         <v>60</v>
@@ -1517,28 +1517,28 @@
         <v>37</v>
       </c>
       <c r="V4" t="n">
-        <v>1.66</v>
+        <v>1.06</v>
       </c>
       <c r="W4" t="n">
-        <v>0.53125</v>
+        <v>0.28125</v>
       </c>
       <c r="X4" t="n">
-        <v>0.53125</v>
+        <v>0.28125</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.125</v>
+        <v>0.083</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.3895</v>
+        <v>0.2515</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.4715</v>
+        <v>0.2405</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.1299</v>
+        <v>0.0898</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.1851</v>
+        <v>0.1082</v>
       </c>
       <c r="AD4" t="n">
         <v>60</v>
@@ -1547,28 +1547,28 @@
         <v>37</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.66</v>
+        <v>1.06</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.53125</v>
+        <v>0.28125</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.53125</v>
+        <v>0.28125</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.125</v>
+        <v>0.083</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.3895</v>
+        <v>0.2515</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.4715</v>
+        <v>0.2405</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.1299</v>
+        <v>0.0898</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.1851</v>
+        <v>0.1082</v>
       </c>
       <c r="AN4" t="n">
         <v>60</v>
@@ -1577,127 +1577,127 @@
         <v>37</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.61</v>
+        <v>0.3</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.66</v>
+        <v>1.06</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.61</v>
+        <v>0.3</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.66</v>
+        <v>1.06</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.61</v>
+        <v>0.3</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.66</v>
+        <v>1.06</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.61</v>
+        <v>0.3</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.66</v>
+        <v>1.06</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.0625</v>
+        <v>0.5625</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.08333</v>
+        <v>0.05556</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.3895</v>
+        <v>0.2515</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.04511</v>
+        <v>0.03007</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.02083</v>
+        <v>0.01389</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.08333</v>
+        <v>0.05556</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.0625</v>
+        <v>0.5625</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.08333</v>
+        <v>0.05556</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.3895</v>
+        <v>0.2515</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.04511</v>
+        <v>0.03007</v>
       </c>
       <c r="BH4" t="n">
-        <v>0.02083</v>
+        <v>0.01389</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.08333</v>
+        <v>0.05556</v>
       </c>
       <c r="BJ4" t="n">
-        <v>1.0625</v>
+        <v>0.5625</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.08333</v>
+        <v>0.05556</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.3895</v>
+        <v>0.2515</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.04511</v>
+        <v>0.03007</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.02083</v>
+        <v>0.01389</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.08333</v>
+        <v>0.05556</v>
       </c>
       <c r="BP4" t="n">
-        <v>1.0625</v>
+        <v>0.5625</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.08333</v>
+        <v>0.05556</v>
       </c>
       <c r="BR4" t="n">
-        <v>0.3895</v>
+        <v>0.2515</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.04511</v>
+        <v>0.03007</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.02083</v>
+        <v>0.01389</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.08333</v>
+        <v>0.05556</v>
       </c>
       <c r="BV4" t="n">
-        <v>1.0625</v>
+        <v>0.5625</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.796</v>
+        <v>0.504</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.796</v>
+        <v>0.504</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.0625</v>
+        <v>0.5625</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.796</v>
+        <v>0.504</v>
       </c>
       <c r="CA4" t="n">
-        <v>0.796</v>
+        <v>0.504</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2650-12-12-12-12-FG</t>
+          <t>2650-06-06-06-06-FG</t>
         </is>
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>Union Cross, 1 1/16-12 JIC x 1 1/16-12 JIC x 1 1/16-12 JIC x 1 1/16-12 JIC</t>
+          <t>Union Cross, 9/16-18 JIC x 9/16-18 JIC x 9/16-18 JIC x 9/16-18 JIC</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
@@ -1707,22 +1707,22 @@
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>1 1/16-12 JIC</t>
+          <t>9/16-18 JIC</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>1 1/16-12 JIC</t>
+          <t>9/16-18 JIC</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>1 1/16-12 JIC</t>
+          <t>9/16-18 JIC</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>1 1/16-12 JIC</t>
+          <t>9/16-18 JIC</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
@@ -1737,44 +1737,44 @@
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> | hex A/F raised from Air-Way 1.06 to 1.0625 (JIC thread major; 2603HX rule)</t>
+          <t>hex A/F raised from Air-Way 0.56 to 0.5625 (JIC thread major; 2603HX rule)</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>2650-12-12-12-12-FG</t>
+          <t>2650-06-06-06-06-FG</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2650-16-16-16-16-FG</t>
+          <t>2650-12-12-12-12-FG</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.81</v>
+        <v>1.66</v>
       </c>
       <c r="C5" t="n">
-        <v>0.65625</v>
+        <v>0.53125</v>
       </c>
       <c r="D5" t="n">
-        <v>0.65625</v>
+        <v>0.53125</v>
       </c>
       <c r="E5" t="n">
         <v>0.125</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4365</v>
+        <v>0.3895</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5965</v>
+        <v>0.4715</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1292</v>
+        <v>0.1299</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1858</v>
+        <v>0.1851</v>
       </c>
       <c r="J5" t="n">
         <v>60</v>
@@ -1783,28 +1783,28 @@
         <v>37</v>
       </c>
       <c r="L5" t="n">
-        <v>1.81</v>
+        <v>1.66</v>
       </c>
       <c r="M5" t="n">
-        <v>0.65625</v>
+        <v>0.53125</v>
       </c>
       <c r="N5" t="n">
-        <v>0.65625</v>
+        <v>0.53125</v>
       </c>
       <c r="O5" t="n">
         <v>0.125</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4365</v>
+        <v>0.3895</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.5965</v>
+        <v>0.4715</v>
       </c>
       <c r="R5" t="n">
-        <v>0.1292</v>
+        <v>0.1299</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1858</v>
+        <v>0.1851</v>
       </c>
       <c r="T5" t="n">
         <v>60</v>
@@ -1813,28 +1813,28 @@
         <v>37</v>
       </c>
       <c r="V5" t="n">
-        <v>1.81</v>
+        <v>1.66</v>
       </c>
       <c r="W5" t="n">
-        <v>0.65625</v>
+        <v>0.53125</v>
       </c>
       <c r="X5" t="n">
-        <v>0.65625</v>
+        <v>0.53125</v>
       </c>
       <c r="Y5" t="n">
         <v>0.125</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.4365</v>
+        <v>0.3895</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.5965</v>
+        <v>0.4715</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.1292</v>
+        <v>0.1299</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.1858</v>
+        <v>0.1851</v>
       </c>
       <c r="AD5" t="n">
         <v>60</v>
@@ -1843,28 +1843,28 @@
         <v>37</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.81</v>
+        <v>1.66</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.65625</v>
+        <v>0.53125</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.65625</v>
+        <v>0.53125</v>
       </c>
       <c r="AI5" t="n">
         <v>0.125</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.4365</v>
+        <v>0.3895</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.5965</v>
+        <v>0.4715</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.1292</v>
+        <v>0.1299</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.1858</v>
+        <v>0.1851</v>
       </c>
       <c r="AN5" t="n">
         <v>60</v>
@@ -1873,37 +1873,37 @@
         <v>37</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.84</v>
+        <v>0.61</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.81</v>
+        <v>1.66</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.84</v>
+        <v>0.61</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.81</v>
+        <v>1.66</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.84</v>
+        <v>0.61</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.81</v>
+        <v>1.66</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.84</v>
+        <v>0.61</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.81</v>
+        <v>1.66</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.3125</v>
+        <v>1.0625</v>
       </c>
       <c r="AY5" t="n">
         <v>0.08333</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.4365</v>
+        <v>0.3895</v>
       </c>
       <c r="BA5" t="n">
         <v>0.04511</v>
@@ -1915,13 +1915,13 @@
         <v>0.08333</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.3125</v>
+        <v>1.0625</v>
       </c>
       <c r="BE5" t="n">
         <v>0.08333</v>
       </c>
       <c r="BF5" t="n">
-        <v>0.4365</v>
+        <v>0.3895</v>
       </c>
       <c r="BG5" t="n">
         <v>0.04511</v>
@@ -1933,13 +1933,13 @@
         <v>0.08333</v>
       </c>
       <c r="BJ5" t="n">
-        <v>1.3125</v>
+        <v>1.0625</v>
       </c>
       <c r="BK5" t="n">
         <v>0.08333</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.4365</v>
+        <v>0.3895</v>
       </c>
       <c r="BM5" t="n">
         <v>0.04511</v>
@@ -1951,13 +1951,13 @@
         <v>0.08333</v>
       </c>
       <c r="BP5" t="n">
-        <v>1.3125</v>
+        <v>1.0625</v>
       </c>
       <c r="BQ5" t="n">
         <v>0.08333</v>
       </c>
       <c r="BR5" t="n">
-        <v>0.4365</v>
+        <v>0.3895</v>
       </c>
       <c r="BS5" t="n">
         <v>0.04511</v>
@@ -1969,74 +1969,370 @@
         <v>0.08333</v>
       </c>
       <c r="BV5" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>0.796</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>0.796</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>0.796</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>0.796</v>
+      </c>
+      <c r="CB5" t="inlineStr">
+        <is>
+          <t>2650-12-12-12-12-FG</t>
+        </is>
+      </c>
+      <c r="CC5" t="inlineStr">
+        <is>
+          <t>Union Cross, 1 1/16-12 JIC x 1 1/16-12 JIC x 1 1/16-12 JIC x 1 1/16-12 JIC</t>
+        </is>
+      </c>
+      <c r="CD5" t="inlineStr">
+        <is>
+          <t>2650</t>
+        </is>
+      </c>
+      <c r="CE5" t="inlineStr">
+        <is>
+          <t>1 1/16-12 JIC</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
+          <t>1 1/16-12 JIC</t>
+        </is>
+      </c>
+      <c r="CG5" t="inlineStr">
+        <is>
+          <t>1 1/16-12 JIC</t>
+        </is>
+      </c>
+      <c r="CH5" t="inlineStr">
+        <is>
+          <t>1 1/16-12 JIC</t>
+        </is>
+      </c>
+      <c r="CI5" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="CJ5" t="inlineStr">
+        <is>
+          <t>Air-Way s203 only (double-pass 13 rows) | MODEL: forged hex body per the 2603HX pattern (Brennan 2603 + 2650 STEPs): hex bars A/F = max(Air-Way hex, male thread majors), flats normal to Z, two continuous bars (X and Y); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="CK5" t="inlineStr">
+        <is>
+          <t>hex A/F raised from Air-Way 1.06 to 1.0625 (JIC thread major; 2603HX rule)</t>
+        </is>
+      </c>
+      <c r="CL5" t="inlineStr">
+        <is>
+          <t>2650-12-12-12-12-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2650-16-16-16-16-FG</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.4365</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.5965</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.1292</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.1858</v>
+      </c>
+      <c r="J6" t="n">
+        <v>60</v>
+      </c>
+      <c r="K6" t="n">
+        <v>37</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.4365</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.5965</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.1292</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.1858</v>
+      </c>
+      <c r="T6" t="n">
+        <v>60</v>
+      </c>
+      <c r="U6" t="n">
+        <v>37</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.4365</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.5965</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.1292</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.1858</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>60</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>37</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0.4365</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0.5965</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0.1292</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0.1858</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>60</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>37</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AX6" t="n">
         <v>1.3125</v>
       </c>
-      <c r="BW5" t="n">
+      <c r="AY6" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0.4365</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>1.3125</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>0.4365</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>1.3125</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>0.4365</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>1.3125</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>0.4365</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>1.3125</v>
+      </c>
+      <c r="BW6" t="n">
         <v>0.899</v>
       </c>
-      <c r="BX5" t="n">
+      <c r="BX6" t="n">
         <v>0.899</v>
       </c>
-      <c r="BY5" t="n">
+      <c r="BY6" t="n">
         <v>1.3125</v>
       </c>
-      <c r="BZ5" t="n">
+      <c r="BZ6" t="n">
         <v>0.899</v>
       </c>
-      <c r="CA5" t="n">
+      <c r="CA6" t="n">
         <v>0.899</v>
       </c>
-      <c r="CB5" t="inlineStr">
+      <c r="CB6" t="inlineStr">
         <is>
           <t>2650-16-16-16-16-FG</t>
         </is>
       </c>
-      <c r="CC5" t="inlineStr">
+      <c r="CC6" t="inlineStr">
         <is>
           <t>Union Cross, 1 5/16-12 JIC x 1 5/16-12 JIC x 1 5/16-12 JIC x 1 5/16-12 JIC</t>
         </is>
       </c>
-      <c r="CD5" t="inlineStr">
+      <c r="CD6" t="inlineStr">
         <is>
           <t>2650</t>
         </is>
       </c>
-      <c r="CE5" t="inlineStr">
+      <c r="CE6" t="inlineStr">
         <is>
           <t>1 5/16-12 JIC</t>
         </is>
       </c>
-      <c r="CF5" t="inlineStr">
+      <c r="CF6" t="inlineStr">
         <is>
           <t>1 5/16-12 JIC</t>
         </is>
       </c>
-      <c r="CG5" t="inlineStr">
+      <c r="CG6" t="inlineStr">
         <is>
           <t>1 5/16-12 JIC</t>
         </is>
       </c>
-      <c r="CH5" t="inlineStr">
+      <c r="CH6" t="inlineStr">
         <is>
           <t>1 5/16-12 JIC</t>
         </is>
       </c>
-      <c r="CI5" t="inlineStr">
+      <c r="CI6" t="inlineStr">
         <is>
           <t>ASSUMED</t>
         </is>
       </c>
-      <c r="CJ5" t="inlineStr">
+      <c r="CJ6" t="inlineStr">
         <is>
           <t>Air-Way s203 only (double-pass 13 rows) | MODEL: forged hex body per the 2603HX pattern (Brennan 2603 + 2650 STEPs): hex bars A/F = max(Air-Way hex, male thread majors), flats normal to Z, two continuous bars (X and Y); hex-end 75deg chamfers and edge fillets NOT modelled; JIC legs: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); Thread feature over THDZ; each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
-      <c r="CK5" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> | hex A/F raised from Air-Way 1.31 to 1.3125 (JIC thread major; 2603HX rule)</t>
-        </is>
-      </c>
-      <c r="CL5" t="inlineStr">
+      <c r="CK6" t="inlineStr">
+        <is>
+          <t>hex A/F raised from Air-Way 1.31 to 1.3125 (JIC thread major; 2603HX rule)</t>
+        </is>
+      </c>
+      <c r="CL6" t="inlineStr">
         <is>
           <t>2650-16-16-16-16-FG</t>
         </is>
